--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2021_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:25</t>
+    <t xml:space="preserve">2026-09-24 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -733,16 +733,16 @@
         <v>0.48</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -756,16 +756,16 @@
         <v>-0.58</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="12">
@@ -779,16 +779,16 @@
         <v>0.63</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -799,16 +799,16 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.54</v>
@@ -851,13 +851,13 @@
         <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.72</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.23</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="16">
@@ -874,13 +874,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.37</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17">
@@ -897,13 +897,13 @@
         <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="18">
